--- a/tuition.xlsx
+++ b/tuition.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76F2F463-F91A-4785-8B94-426597A418BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AF39DDB-73F8-4AB3-B969-9E2DF26D513A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="61">
   <si>
     <t>الطب البشري</t>
   </si>
@@ -99,9 +99,6 @@
     <t>لوجستيات النقل الدولي</t>
   </si>
   <si>
-    <t>-----</t>
-  </si>
-  <si>
     <t>الفنون التطبيقية</t>
   </si>
   <si>
@@ -165,40 +162,52 @@
     <t>التمويل</t>
   </si>
   <si>
-    <t>2,500‎</t>
-  </si>
-  <si>
-    <t>…</t>
-  </si>
-  <si>
-    <t>2,700‎</t>
-  </si>
-  <si>
     <t>50</t>
   </si>
   <si>
-    <t>45</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>1050</t>
-  </si>
-  <si>
-    <t>640</t>
-  </si>
-  <si>
-    <t>400</t>
-  </si>
-  <si>
     <t>`</t>
+  </si>
+  <si>
+    <t>250</t>
+  </si>
+  <si>
+    <t>200</t>
+  </si>
+  <si>
+    <t>120</t>
+  </si>
+  <si>
+    <t>90</t>
+  </si>
+  <si>
+    <t>140</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>115</t>
+  </si>
+  <si>
+    <t>80</t>
+  </si>
+  <si>
+    <t>2800</t>
+  </si>
+  <si>
+    <t>4800</t>
+  </si>
+  <si>
+    <t>5200</t>
+  </si>
+  <si>
+    <t>1650</t>
+  </si>
+  <si>
+    <t>1750</t>
+  </si>
+  <si>
+    <t>1000</t>
   </si>
 </sst>
 </file>
@@ -252,7 +261,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -261,9 +270,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -560,23 +566,23 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="31.5703125" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" style="6"/>
-    <col min="3" max="3" width="12.42578125" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.140625" style="6"/>
+    <col min="2" max="2" width="9.140625" style="5"/>
+    <col min="3" max="3" width="12.42578125" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.140625" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="C1" s="5">
+      <c r="B1" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1" s="4">
         <v>2250</v>
       </c>
-      <c r="D1" s="5">
-        <v>11250</v>
+      <c r="D1" s="4" t="s">
+        <v>47</v>
       </c>
       <c r="E1" s="1"/>
     </row>
@@ -584,14 +590,14 @@
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="C2" s="5">
-        <v>1665</v>
-      </c>
-      <c r="D2" s="5">
-        <v>7400</v>
+      <c r="B2" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>48</v>
       </c>
       <c r="E2" s="1"/>
     </row>
@@ -599,14 +605,14 @@
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="C3" s="5">
-        <v>1400</v>
-      </c>
-      <c r="D3" s="5">
-        <v>6125</v>
+      <c r="B3" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>48</v>
       </c>
       <c r="E3" s="1"/>
     </row>
@@ -614,14 +620,14 @@
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="C4" s="5">
-        <v>1050</v>
-      </c>
-      <c r="D4" s="5">
-        <v>3500</v>
+      <c r="B4" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>49</v>
       </c>
       <c r="E4" s="1"/>
     </row>
@@ -629,29 +635,29 @@
       <c r="A5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="C5" s="5">
-        <v>1050</v>
-      </c>
-      <c r="D5" s="5">
-        <v>3500</v>
+      <c r="B5" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>49</v>
       </c>
       <c r="E5" s="1"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="C6" s="5">
-        <v>1050</v>
-      </c>
-      <c r="D6" s="5">
-        <v>3500</v>
+        <v>43</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>49</v>
       </c>
       <c r="E6" s="1"/>
     </row>
@@ -659,14 +665,14 @@
       <c r="A7" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="C7" s="5">
-        <v>1050</v>
-      </c>
-      <c r="D7" s="5">
-        <v>3500</v>
+      <c r="B7" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>49</v>
       </c>
       <c r="E7" s="1"/>
     </row>
@@ -674,14 +680,14 @@
       <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="C8" s="5">
-        <v>1050</v>
-      </c>
-      <c r="D8" s="5">
-        <v>3500</v>
+      <c r="B8" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>49</v>
       </c>
       <c r="E8" s="1"/>
     </row>
@@ -689,14 +695,14 @@
       <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="C9" s="5">
-        <v>1050</v>
-      </c>
-      <c r="D9" s="5">
-        <v>3500</v>
+      <c r="B9" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>49</v>
       </c>
       <c r="E9" s="1"/>
     </row>
@@ -704,14 +710,14 @@
       <c r="A10" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="C10" s="5">
-        <v>1050</v>
-      </c>
-      <c r="D10" s="5">
-        <v>3500</v>
+      <c r="B10" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>49</v>
       </c>
       <c r="E10" s="1"/>
     </row>
@@ -719,14 +725,14 @@
       <c r="A11" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="C11" s="5">
-        <v>1050</v>
-      </c>
-      <c r="D11" s="5">
-        <v>3500</v>
+      <c r="B11" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>49</v>
       </c>
       <c r="E11" s="1"/>
     </row>
@@ -734,14 +740,14 @@
       <c r="A12" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B12" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="C12" s="5">
-        <v>1050</v>
-      </c>
-      <c r="D12" s="5">
-        <v>3500</v>
+      <c r="B12" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>49</v>
       </c>
       <c r="E12" s="1"/>
     </row>
@@ -749,14 +755,14 @@
       <c r="A13" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C13" s="5">
-        <v>640</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>46</v>
+      <c r="B13" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>50</v>
       </c>
       <c r="E13" s="1"/>
     </row>
@@ -764,14 +770,14 @@
       <c r="A14" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C14" s="5">
-        <v>700</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>48</v>
+      <c r="B14" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>50</v>
       </c>
       <c r="E14" s="1"/>
     </row>
@@ -779,14 +785,14 @@
       <c r="A15" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C15" s="5">
-        <v>640</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>46</v>
+      <c r="B15" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>50</v>
       </c>
       <c r="E15" s="1"/>
     </row>
@@ -794,14 +800,14 @@
       <c r="A16" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C16" s="5">
-        <v>640</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>46</v>
+      <c r="B16" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>50</v>
       </c>
       <c r="E16" s="1"/>
     </row>
@@ -809,14 +815,14 @@
       <c r="A17" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C17" s="5">
-        <v>640</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>46</v>
+      <c r="B17" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>50</v>
       </c>
       <c r="E17" s="1"/>
     </row>
@@ -824,14 +830,14 @@
       <c r="A18" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B18" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>27</v>
+      <c r="B18" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>26</v>
       </c>
       <c r="E18" s="1"/>
     </row>
@@ -839,14 +845,14 @@
       <c r="A19" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B19" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>27</v>
+      <c r="B19" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>26</v>
       </c>
       <c r="E19" s="1"/>
     </row>
@@ -854,14 +860,14 @@
       <c r="A20" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B20" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>27</v>
+      <c r="B20" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>26</v>
       </c>
       <c r="E20" s="1"/>
     </row>
@@ -869,14 +875,14 @@
       <c r="A21" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B21" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>27</v>
+      <c r="B21" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>26</v>
       </c>
       <c r="E21" s="1"/>
     </row>
@@ -884,14 +890,14 @@
       <c r="A22" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B22" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>27</v>
+      <c r="B22" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>26</v>
       </c>
       <c r="E22" s="1"/>
     </row>
@@ -899,14 +905,14 @@
       <c r="A23" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B23" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>27</v>
+      <c r="B23" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>26</v>
       </c>
       <c r="E23" s="1"/>
     </row>
@@ -914,14 +920,14 @@
       <c r="A24" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B24" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>27</v>
+      <c r="B24" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>26</v>
       </c>
       <c r="E24" s="1"/>
     </row>
@@ -929,218 +935,218 @@
       <c r="A25" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>27</v>
+      <c r="B25" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>26</v>
       </c>
       <c r="E25" s="1"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>27</v>
+        <v>24</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>26</v>
       </c>
       <c r="E26" s="1"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B27" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D27" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>26</v>
       </c>
       <c r="E27" s="1"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C28" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="D28" s="6" t="s">
-        <v>27</v>
+      <c r="B28" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>26</v>
       </c>
       <c r="E28" s="1"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B29" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C29" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="D29" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>26</v>
       </c>
       <c r="E29" s="1"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B30" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C30" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D30" s="6" t="s">
-        <v>27</v>
+        <v>29</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>26</v>
       </c>
       <c r="E30" s="1"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B31" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C31" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D31" s="6" t="s">
-        <v>27</v>
+        <v>30</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>26</v>
       </c>
       <c r="E31" s="1"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="C32" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B32" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="D32" s="5">
-        <v>3500</v>
+      <c r="C32" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>49</v>
       </c>
       <c r="E32" s="1"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B33" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C33" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D33" s="6" t="s">
-        <v>27</v>
+        <v>32</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B34" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C34" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D34" s="6" t="s">
-        <v>27</v>
+        <v>33</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B35" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C35" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D35" s="6" t="s">
-        <v>27</v>
+        <v>34</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B36" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C36" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D36" s="6" t="s">
-        <v>27</v>
+        <v>35</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B37" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C37" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D37" s="6" t="s">
-        <v>27</v>
+        <v>36</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B38" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C38" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D38" s="6" t="s">
-        <v>27</v>
+        <v>37</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B39" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C39" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D39" s="6" t="s">
-        <v>27</v>
+        <v>38</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>26</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="1"/>
@@ -1148,88 +1154,88 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B40" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C40" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="D40" s="6" t="s">
-        <v>27</v>
+        <v>39</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B41" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="C41" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B41" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="D41" s="5">
-        <v>3500</v>
+      <c r="C41" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>49</v>
       </c>
       <c r="E41" s="1"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B42" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C42" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D42" s="6" t="s">
-        <v>27</v>
+        <v>24</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B43" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C43" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D43" s="6" t="s">
-        <v>27</v>
+        <v>41</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B44" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="C44" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B44" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="D44" s="5">
-        <v>3500</v>
+      <c r="C44" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>49</v>
       </c>
       <c r="E44" s="1"/>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B45" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C45" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D45" s="6" t="s">
-        <v>27</v>
+        <v>44</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/tuition.xlsx
+++ b/tuition.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AF39DDB-73F8-4AB3-B969-9E2DF26D513A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A6FF035-9FF6-4501-99D5-095D08D74239}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="62">
   <si>
     <t>الطب البشري</t>
   </si>
@@ -208,6 +208,9 @@
   </si>
   <si>
     <t>1000</t>
+  </si>
+  <si>
+    <t>7800</t>
   </si>
 </sst>
 </file>
@@ -578,8 +581,8 @@
       <c r="B1" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="C1" s="4">
-        <v>2250</v>
+      <c r="C1" s="4" t="s">
+        <v>61</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>47</v>
